--- a/MainTop/27.12.2025 бирки/27.12.2025 бирки.xlsx
+++ b/MainTop/27.12.2025 бирки/27.12.2025 бирки.xlsx
@@ -5,28 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maxim\Documents\GitHub\Ozon_upload\MainTop\27.12.2025 бирки\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\27.12.2025 бирки\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD833936-43F3-4A3F-9463-010AF6643CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD99FD0-A186-4846-B7AA-541D46951910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -78,10 +67,10 @@
     <t>Термобирки Пиксар Дисней</t>
   </si>
   <si>
-    <t>количество</t>
-  </si>
-  <si>
     <t>27.12.2025 бирки</t>
+  </si>
+  <si>
+    <t>Num_Copies</t>
   </si>
 </sst>
 </file>
@@ -457,7 +446,7 @@
   <cols>
     <col min="1" max="1" width="31.7109375" customWidth="1"/>
     <col min="2" max="4" width="5.7109375" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -468,10 +457,10 @@
       <c r="C1" s="3"/>
       <c r="D1" s="2"/>
       <c r="E1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
         <v>15</v>
-      </c>
-      <c r="F1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -742,22 +731,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="B16" s="6">
-        <f>SUM(B2:B15)</f>
-        <v>527</v>
-      </c>
-      <c r="C16" s="6">
-        <f t="shared" ref="C16:E16" si="2">SUM(C2:C15)</f>
-        <v>13</v>
-      </c>
-      <c r="D16" s="6">
-        <f t="shared" si="2"/>
-        <v>540</v>
-      </c>
-      <c r="E16" s="6">
-        <f t="shared" si="2"/>
-        <v>135</v>
-      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C17" s="1"/>
